--- a/table/supp/workbooks/SuppTable_S4_Class_composition_and_contrasts.xlsx
+++ b/table/supp/workbooks/SuppTable_S4_Class_composition_and_contrasts.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t xml:space="preserve">Level</t>
   </si>
@@ -191,9 +191,6 @@
   </si>
   <si>
     <t xml:space="preserve">significance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jackknife_stability</t>
   </si>
   <si>
     <t xml:space="preserve">MG/SQDG</t>
@@ -4432,13 +4429,10 @@
       <c r="K1" t="s">
         <v>57</v>
       </c>
-      <c r="L1" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" t="n">
         <v>394</v>
@@ -4459,7 +4453,7 @@
         <v>4.96</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
@@ -4468,15 +4462,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" t="n">
         <v>394</v>
@@ -4497,7 +4488,7 @@
         <v>3.67</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
@@ -4506,15 +4497,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" t="n">
         <v>394</v>
@@ -4535,7 +4523,7 @@
         <v>12.71</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I4" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
@@ -4544,15 +4532,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" t="n">
         <v>394</v>
@@ -4573,7 +4558,7 @@
         <v>0.38</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
@@ -4582,15 +4567,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
         <v>394</v>
@@ -4611,7 +4593,7 @@
         <v>2.63</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I6" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000411</v>
@@ -4620,15 +4602,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" t="n">
         <v>394</v>
@@ -4649,7 +4628,7 @@
         <v>0.34</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I7" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
@@ -4658,15 +4637,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" t="n">
         <v>394</v>
@@ -4687,7 +4663,7 @@
         <v>2.76</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I8" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427</v>
@@ -4696,15 +4672,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B9" t="n">
         <v>394</v>
@@ -4725,7 +4698,7 @@
         <v>0.13</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I9" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000489</v>
@@ -4734,15 +4707,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="n">
         <v>394</v>
@@ -4763,7 +4733,7 @@
         <v>0.3</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I10" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427</v>
@@ -4772,15 +4742,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" t="n">
         <v>394</v>
@@ -4801,7 +4768,7 @@
         <v>9.34</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I11" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000478</v>
@@ -4810,15 +4777,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" t="n">
         <v>394</v>
@@ -4839,7 +4803,7 @@
         <v>7.95</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I12" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000489</v>
@@ -4848,15 +4812,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" t="n">
         <v>394</v>
@@ -4877,7 +4838,7 @@
         <v>0.11</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I13" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000611</v>
@@ -4886,15 +4847,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" t="n">
         <v>394</v>
@@ -4915,7 +4873,7 @@
         <v>0.15</v>
       </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000819</v>
@@ -4924,15 +4882,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" t="n">
         <v>394</v>
@@ -4953,7 +4908,7 @@
         <v>0.18</v>
       </c>
       <c r="H15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I15" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000838</v>
@@ -4962,15 +4917,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="n">
         <v>394</v>
@@ -4991,7 +4943,7 @@
         <v>3.82</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I16" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000727</v>
@@ -5000,15 +4952,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" t="n">
         <v>394</v>
@@ -5029,7 +4978,7 @@
         <v>5.71</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I17" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000838</v>
@@ -5038,15 +4987,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
       </c>
       <c r="K17" t="s">
-        <v>61</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" t="n">
         <v>394</v>
@@ -5067,7 +5013,7 @@
         <v>1.92</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I18" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000224</v>
@@ -5076,15 +5022,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000434</v>
       </c>
       <c r="K18" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" t="n">
         <v>394</v>
@@ -5105,7 +5048,7 @@
         <v>0.52</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I19" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000275</v>
@@ -5114,15 +5057,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000453</v>
       </c>
       <c r="K19" t="s">
-        <v>61</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" t="n">
         <v>394</v>
@@ -5143,7 +5083,7 @@
         <v>0.38</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I20" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000026</v>
@@ -5152,15 +5092,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000453</v>
       </c>
       <c r="K20" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" t="n">
         <v>394</v>
@@ -5181,7 +5118,7 @@
         <v>1.91</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I21" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000275</v>
@@ -5190,15 +5127,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000453</v>
       </c>
       <c r="K21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" t="n">
         <v>394</v>
@@ -5219,7 +5153,7 @@
         <v>0.07</v>
       </c>
       <c r="H22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I22" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000459</v>
@@ -5228,15 +5162,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000721</v>
       </c>
       <c r="K22" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" t="n">
         <v>394</v>
@@ -5257,7 +5188,7 @@
         <v>0.23</v>
       </c>
       <c r="H23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I23" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000568</v>
@@ -5266,15 +5197,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000852</v>
       </c>
       <c r="K23" t="s">
-        <v>61</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B24" t="n">
         <v>394</v>
@@ -5295,7 +5223,7 @@
         <v>0.21</v>
       </c>
       <c r="H24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I24" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000108</v>
@@ -5304,15 +5232,12 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000154</v>
       </c>
       <c r="K24" t="s">
-        <v>61</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" t="n">
         <v>394</v>
@@ -5333,7 +5258,7 @@
         <v>2.29</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000754</v>
@@ -5342,15 +5267,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104</v>
       </c>
       <c r="K25" t="s">
-        <v>61</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B26" t="n">
         <v>394</v>
@@ -5371,7 +5293,7 @@
         <v>0.48</v>
       </c>
       <c r="H26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I26" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000152</v>
@@ -5380,15 +5302,12 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000201</v>
       </c>
       <c r="K26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B27" t="n">
         <v>394</v>
@@ -5409,7 +5328,7 @@
         <v>0.28</v>
       </c>
       <c r="H27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I27" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000355</v>
@@ -5418,15 +5337,12 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000045</v>
       </c>
       <c r="K27" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" t="n">
         <v>394</v>
@@ -5447,7 +5363,7 @@
         <v>2.75</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I28" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000402</v>
@@ -5456,15 +5372,12 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000491</v>
       </c>
       <c r="K28" t="s">
-        <v>61</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" t="n">
         <v>394</v>
@@ -5485,7 +5398,7 @@
         <v>2.7</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I29" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000217</v>
@@ -5494,15 +5407,12 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000256</v>
       </c>
       <c r="K29" t="s">
-        <v>61</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" t="n">
         <v>394</v>
@@ -5523,7 +5433,7 @@
         <v>2.16</v>
       </c>
       <c r="H30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I30" t="n">
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000617</v>
@@ -5532,15 +5442,12 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000702</v>
       </c>
       <c r="K30" t="s">
-        <v>61</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" t="n">
         <v>394</v>
@@ -5561,7 +5468,7 @@
         <v>1.34</v>
       </c>
       <c r="H31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31" t="n">
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000153</v>
@@ -5570,15 +5477,12 @@
         <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168</v>
       </c>
       <c r="K31" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B32" t="n">
         <v>394</v>
@@ -5599,7 +5503,7 @@
         <v>2.9</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I32" t="n">
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000721</v>
@@ -5608,15 +5512,12 @@
         <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000768</v>
       </c>
       <c r="K32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" t="n">
         <v>394</v>
@@ -5637,7 +5538,7 @@
         <v>0.74</v>
       </c>
       <c r="H33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I33" t="n">
         <v>0.0000000000000000000000000000000000000000000221</v>
@@ -5646,15 +5547,12 @@
         <v>0.0000000000000000000000000000000000000000000228</v>
       </c>
       <c r="K33" t="s">
-        <v>61</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" t="n">
         <v>394</v>
@@ -5675,7 +5573,7 @@
         <v>1.3</v>
       </c>
       <c r="H34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I34" t="n">
         <v>0.0000000000000000644</v>
@@ -5684,10 +5582,7 @@
         <v>0.0000000000000000644</v>
       </c>
       <c r="K34" t="s">
-        <v>61</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5706,27 +5601,27 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
         <v>95</v>
-      </c>
-      <c r="C1" t="s">
-        <v>96</v>
       </c>
       <c r="D1" t="s">
         <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -5737,13 +5632,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -5754,13 +5649,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -5771,13 +5666,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -5788,13 +5683,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -5805,13 +5700,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -5822,13 +5717,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -5839,13 +5734,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -5856,13 +5751,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -5873,13 +5768,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -5890,13 +5785,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -5907,13 +5802,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -5924,13 +5819,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -5941,13 +5836,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -5958,13 +5853,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
         <v>8</v>
@@ -5975,13 +5870,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
@@ -5992,13 +5887,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -6009,13 +5904,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
@@ -6026,13 +5921,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -6043,13 +5938,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B21" t="n">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>

--- a/table/supp/workbooks/SuppTable_S4_Class_composition_and_contrasts.xlsx
+++ b/table/supp/workbooks/SuppTable_S4_Class_composition_and_contrasts.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t xml:space="preserve">Level</t>
   </si>
@@ -31,18 +31,39 @@
     <t xml:space="preserve">pct_TIC</t>
   </si>
   <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatty Acyls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycerolipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycerophospholipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prenol Lipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingolipids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sterol Lipids</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lipid class</t>
   </si>
   <si>
     <t xml:space="preserve">DG</t>
   </si>
   <si>
-    <t xml:space="preserve">CTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIN</t>
-  </si>
-  <si>
     <t xml:space="preserve">DGDG</t>
   </si>
   <si>
@@ -82,36 +103,6 @@
     <t xml:space="preserve">TG</t>
   </si>
   <si>
-    <t xml:space="preserve">Superclass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Betaine lipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ether lipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatty acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycerolipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glycerophospholipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prenol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sphingolipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terpenoid</t>
-  </si>
-  <si>
     <t xml:space="preserve">Class</t>
   </si>
   <si>
@@ -127,7 +118,7 @@
     <t xml:space="preserve">AbsEffect</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature</t>
+    <t xml:space="preserve">FoldChange</t>
   </si>
   <si>
     <t xml:space="preserve">Class_A</t>
@@ -193,112 +184,112 @@
     <t xml:space="preserve">significance</t>
   </si>
   <si>
+    <t xml:space="preserve">PS/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LI &gt; C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">****</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPE/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQDG/TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LI &lt; C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS/PC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDG/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS/DG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPE/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA/PS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC/LPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC/SQDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG/DG</t>
+  </si>
+  <si>
     <t xml:space="preserve">MG/SQDG</t>
   </si>
   <si>
-    <t xml:space="preserve">LI &gt; C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">***</t>
+    <t xml:space="preserve">TG/PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG/PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE/PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPC/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGDG/PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/MGDG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGDG/MG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGDG/PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG/DGDG</t>
   </si>
   <si>
     <t xml:space="preserve">MG/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGDG/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LI &lt; C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DG/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/DG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGDG/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPE/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS/PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MG/PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGDG/PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPC/LPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/PS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC/SQDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGDG/PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQDG/TG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPE/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/MGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/DG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PG/DGDG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE/PA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TG/PE</t>
   </si>
   <si>
     <t xml:space="preserve">Rank</t>
@@ -706,7 +697,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>12.9792403228336</v>
+        <v>0.660503349072862</v>
       </c>
     </row>
     <row r="3">
@@ -720,7 +711,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>13.7943332910046</v>
+        <v>0.416201956551322</v>
       </c>
     </row>
     <row r="4">
@@ -734,7 +725,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>12.083589996121</v>
+        <v>65.4121078239608</v>
       </c>
     </row>
     <row r="5">
@@ -748,7 +739,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>12.2068464193104</v>
+        <v>64.3429658336047</v>
       </c>
     </row>
     <row r="6">
@@ -762,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.150325521955846</v>
+        <v>30.3345635718484</v>
       </c>
     </row>
     <row r="7">
@@ -776,7 +767,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0.154492987229385</v>
+        <v>30.6937496433726</v>
       </c>
     </row>
     <row r="8">
@@ -790,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00646658279399933</v>
+        <v>3.42000664103267</v>
       </c>
     </row>
     <row r="9">
@@ -804,7 +795,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0139218279850754</v>
+        <v>4.16852766141525</v>
       </c>
     </row>
     <row r="10">
@@ -818,7 +809,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.30194400394028</v>
+        <v>0.130712572828313</v>
       </c>
     </row>
     <row r="11">
@@ -832,7 +823,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0512407127772</v>
+        <v>0.161903219018698</v>
       </c>
     </row>
     <row r="12">
@@ -846,7 +837,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>32.6840505592754</v>
+        <v>0.0421060412569125</v>
       </c>
     </row>
     <row r="13">
@@ -860,469 +851,399 @@
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>30.0658825707473</v>
+        <v>0.216651686037459</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5.30140026426419</v>
+        <v>12.9792403228336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6.53194597906461</v>
+        <v>13.7943332910046</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.016789256062105</v>
+        <v>12.083589996121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0256000619625351</v>
+        <v>12.2068464193104</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>24.2211743677781</v>
+        <v>0.150325521955846</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>23.2824609907854</v>
+        <v>0.154492987229385</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5.54303664167746</v>
+        <v>0.00646658279399933</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>6.21172084286869</v>
+        <v>0.0139218279850754</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.380524053808567</v>
+        <v>1.30194400394028</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>0.44504631643678</v>
+        <v>1.0512407127772</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0141575519437136</v>
+        <v>32.6840505592754</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0449518354297121</v>
+        <v>30.0658825707473</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.75130568404306</v>
+        <v>5.3014002642642</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>1.27610717010143</v>
+        <v>6.53194597906461</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.56599519350257</v>
+        <v>0.016789256062105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>4.8954489942969</v>
+        <v>0.0256000619625351</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00060792593337868</v>
+        <v>24.2211743677781</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>1.00303807751483</v>
+        <v>23.2824609907854</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.953217540176834</v>
+        <v>5.54303664167746</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>0.660503349072863</v>
+        <v>6.21172084286869</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.416201956551322</v>
+        <v>0.380524053808567</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>64.409069746446</v>
+        <v>0.445046316436781</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
         <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>63.3891403674944</v>
+        <v>0.0141575519437136</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>30.3345635718485</v>
+        <v>0.0449518354297121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>30.6937496433726</v>
+        <v>2.75130568404306</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.138296356020255</v>
+        <v>1.27610717010143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
         <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.193367727843116</v>
+        <v>2.56599519350257</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>0.130712572828313</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>21</v>
-      </c>
-      <c r="B42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.161903219018698</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.0421060412569126</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.216651686037459</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" t="n">
-        <v>3.28171028501242</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3.97515993357213</v>
+        <v>4.8954489942969</v>
       </c>
     </row>
   </sheetData>
@@ -1338,240 +1259,282 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.150020827009663</v>
+        <v>1.01679180751706</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.16524305036448</v>
+        <v>0.963345098556201</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.134798037595973</v>
+        <v>1.06783290688334</v>
       </c>
       <c r="E2" t="n">
-        <v>0.150020827009663</v>
+        <v>1.01679180751706</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.76431207767127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.200027470991742</v>
+        <v>-0.942084768792643</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.212317603452343</v>
+        <v>-0.960422158596724</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.186109298305702</v>
+        <v>-0.923003273268884</v>
       </c>
       <c r="E3" t="n">
-        <v>0.200027470991742</v>
+        <v>0.942084768792643</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.389814314933473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>0.264109961706918</v>
+        <v>0.606787664895789</v>
       </c>
       <c r="C4" t="n">
-        <v>0.23228752514973</v>
+        <v>0.57643459802212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.297229580727586</v>
+        <v>0.636077378592577</v>
       </c>
       <c r="E4" t="n">
-        <v>0.264109961706918</v>
+        <v>0.606787664895789</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.83452880202761</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>0.571618014808936</v>
+        <v>0.476795091624303</v>
       </c>
       <c r="C5" t="n">
-        <v>0.542593573629583</v>
+        <v>0.444514374205478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.601554845744906</v>
+        <v>0.507016311174211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.571618014808936</v>
+        <v>0.476795091624303</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.61090332264983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.422867492265213</v>
+        <v>-0.387697842178366</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.436993826834222</v>
+        <v>-0.400973681333276</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.409233760628579</v>
+        <v>-0.373329791362068</v>
       </c>
       <c r="E6" t="n">
-        <v>0.422867492265213</v>
+        <v>0.387697842178366</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.678617361832337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.292563486577049</v>
+        <v>-0.257393836490201</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.309395619346519</v>
+        <v>-0.273108899213287</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.274619839600066</v>
+        <v>-0.239853896338556</v>
       </c>
       <c r="E7" t="n">
-        <v>0.292563486577049</v>
+        <v>0.257393836490201</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.773063693112115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
-        <v>0.161364465821687</v>
+        <v>-0.217351018084144</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0802791032221784</v>
+        <v>-0.240708283740906</v>
       </c>
       <c r="D8" t="n">
-        <v>0.234224915403812</v>
+        <v>-0.192543403384832</v>
       </c>
       <c r="E8" t="n">
-        <v>0.161364465821687</v>
+        <v>0.217351018084144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.804647473912702</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.2550848711275</v>
+        <v>0.196534115908537</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.280081962268929</v>
+        <v>0.120264423197661</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.228859486098846</v>
+        <v>0.262478004623756</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2550848711275</v>
+        <v>0.196534115908537</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.21717684526379</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0994667518395242</v>
+        <v>-0.164857820904893</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.120469491673995</v>
+        <v>-0.176975660017586</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0771711765867226</v>
+        <v>-0.150610465641452</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0994667518395242</v>
+        <v>0.164857820904893</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.848014265417958</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0468606941547983</v>
+        <v>-0.138396589272123</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0626829577178799</v>
+        <v>-0.165203860740266</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0300293830228002</v>
+        <v>-0.11049119128913</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0468606941547983</v>
+        <v>0.138396589272123</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.870753291845166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>0.981622157430208</v>
+        <v>-0.113730552131991</v>
       </c>
       <c r="C12" t="n">
-        <v>0.930662382987049</v>
+        <v>-0.128339441748043</v>
       </c>
       <c r="D12" t="n">
-        <v>1.02877600119312</v>
+        <v>-0.0977038079204138</v>
       </c>
       <c r="E12" t="n">
-        <v>0.981622157430208</v>
+        <v>0.113730552131991</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.892498405279169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.977254418879491</v>
+        <v>-0.0637052080233771</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.995272795070058</v>
+        <v>-0.0869272162166274</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.958675119636243</v>
+        <v>-0.0419363782991806</v>
       </c>
       <c r="E13" t="n">
-        <v>0.977254418879491</v>
+        <v>0.0637052080233771</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.938281556640029</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B14" t="n">
-        <v>0.465431413077217</v>
+        <v>-0.0116910440679509</v>
       </c>
       <c r="C14" t="n">
-        <v>0.429984680387574</v>
+        <v>-0.0261171994836666</v>
       </c>
       <c r="D14" t="n">
-        <v>0.500430485987658</v>
+        <v>0.00358719446786396</v>
       </c>
       <c r="E14" t="n">
-        <v>0.465431413077217</v>
+        <v>0.0116910440679509</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.98837703064135</v>
       </c>
     </row>
   </sheetData>
@@ -1587,142 +1550,142 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>33</v>
-      </c>
-      <c r="D1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.615452240086883</v>
+        <v>-1.41887986041695</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.653130916472164</v>
+        <v>-1.4548410584564</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.581285103683464</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
+        <v>-1.38043961352675</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.41887986041695</v>
       </c>
       <c r="F2" t="n">
-        <v>0.615452240086883</v>
+        <v>0.241984922032599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.665458884068959</v>
+        <v>-0.864492933802669</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.700944439846832</v>
+        <v>-0.896464567053855</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.630005272164145</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
+        <v>-0.829201288126029</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.864492933802669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.665458884068959</v>
+        <v>0.421265107775715</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.201321451370302</v>
+        <v>-0.734188928114504</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.25368427457623</v>
+        <v>-0.768133830419512</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.154054489138711</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
+        <v>-0.696850694346989</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.734188928114504</v>
       </c>
       <c r="F4" t="n">
-        <v>0.201321451370302</v>
+        <v>0.47989453013262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
-        <v>0.106186601731723</v>
+        <v>-0.694146109708447</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0576921182187917</v>
+        <v>-0.735344685091511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.156454134979322</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
+        <v>-0.649983897229075</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.694146109708447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.106186601731723</v>
+        <v>0.499500784807565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.888298905342432</v>
+        <v>-0.641652912529196</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.92524393432472</v>
+        <v>-0.672671815989876</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.853594780281304</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
+        <v>-0.606450884643303</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.641652912529196</v>
       </c>
       <c r="F6" t="n">
-        <v>0.888298905342432</v>
+        <v>0.526421575705134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.757994899654264</v>
+        <v>-0.615191680896426</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.795987872993537</v>
+        <v>-0.661244145122262</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.721515449950697</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
+        <v>-0.566635759040863</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.615191680896426</v>
       </c>
       <c r="F7" t="n">
-        <v>0.757994899654264</v>
+        <v>0.540537274709221</v>
       </c>
     </row>
     <row r="8">
@@ -1730,119 +1693,119 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.304066947255529</v>
+        <v>-0.590525643756294</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.391358314681927</v>
+        <v>-0.621757626033544</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.223279070637291</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
+        <v>-0.555777566363953</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.590525643756294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.304066947255529</v>
+        <v>0.554035982625617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.720516284204718</v>
+        <v>-0.54050029964768</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.764458502314933</v>
+        <v>-0.577896949302591</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.677788461243583</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
+        <v>-0.49777145837224</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.54050029964768</v>
       </c>
       <c r="F9" t="n">
-        <v>0.720516284204718</v>
+        <v>0.582456776547347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.564898164916742</v>
+        <v>0.539996715892756</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.604270191599795</v>
+        <v>0.480657206539488</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.527738341068441</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
+        <v>0.597447522236217</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.539996715892756</v>
       </c>
       <c r="F10" t="n">
-        <v>0.564898164916742</v>
+        <v>1.71600122664355</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.512292107232015</v>
+        <v>-0.488486135692254</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.551994586240224</v>
+        <v>-0.524684265083625</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.478591627102836</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
+        <v>-0.44656089467468</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.488486135692254</v>
       </c>
       <c r="F11" t="n">
-        <v>0.512292107232015</v>
+        <v>0.613554529774969</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
-        <v>0.516190744352994</v>
+        <v>-0.280260975715766</v>
       </c>
       <c r="C12" t="n">
-        <v>0.454007095361774</v>
+        <v>-0.366804865395598</v>
       </c>
       <c r="D12" t="n">
-        <v>0.573468179493469</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
+        <v>-0.188516372799127</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.280260975715766</v>
       </c>
       <c r="F12" t="n">
-        <v>0.516190744352994</v>
+        <v>0.755586525988178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.44268583195671</v>
+        <v>0.129992573271486</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.48445149988038</v>
+        <v>0.0804270845089133</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4024851678621</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
+        <v>0.173259329533849</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.129992573271486</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44268583195671</v>
+        <v>1.1388199255868</v>
       </c>
     </row>
   </sheetData>
@@ -1858,42 +1821,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>43</v>
-      </c>
-      <c r="H1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>0.445425942298677</v>
@@ -1922,10 +1885,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
         <v>-0.258015528607829</v>
@@ -1954,10 +1917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>-0.412050008620979</v>
@@ -1986,10 +1949,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>0.102802200550213</v>
@@ -2018,10 +1981,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>-0.539949178901385</v>
@@ -2050,10 +2013,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>-0.11794078371344</v>
@@ -2082,10 +2045,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>0.127166105714794</v>
@@ -2114,10 +2077,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>0.0491513037488628</v>
@@ -2146,10 +2109,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>-0.0469751726884139</v>
@@ -2178,10 +2141,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>0.0122707783582706</v>
@@ -2210,10 +2173,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>-0.0352137777613839</v>
@@ -2242,10 +2205,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>-0.236552719881628</v>
@@ -2274,10 +2237,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>-0.235819748997672</v>
@@ -2306,10 +2269,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>-0.420164870185783</v>
@@ -2338,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
         <v>-0.401393484506365</v>
@@ -2370,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>-0.445140161042946</v>
@@ -2402,10 +2365,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>-0.244443515724674</v>
@@ -2434,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>-0.0772738508146577</v>
@@ -2466,10 +2429,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
         <v>0.0944744301567859</v>
@@ -2498,10 +2461,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
         <v>-0.277417839202953</v>
@@ -2530,10 +2493,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
         <v>0.231736226126446</v>
@@ -2562,10 +2525,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C23" t="n">
         <v>-0.584273760505069</v>
@@ -2594,10 +2557,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C24" t="n">
         <v>-0.369994588922748</v>
@@ -2626,10 +2589,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C25" t="n">
         <v>-0.081205625031116</v>
@@ -2658,10 +2621,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
         <v>-0.227061497005428</v>
@@ -2690,10 +2653,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
         <v>-0.0897957986804975</v>
@@ -2722,10 +2685,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C28" t="n">
         <v>-0.441745057878795</v>
@@ -2754,10 +2717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
         <v>-0.0565777352959691</v>
@@ -2786,10 +2749,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C30" t="n">
         <v>0.0366088069256805</v>
@@ -2818,10 +2781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C31" t="n">
         <v>-0.255158627064199</v>
@@ -2850,10 +2813,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C32" t="n">
         <v>0.25698639546051</v>
@@ -2882,10 +2845,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C33" t="n">
         <v>-0.509483213639671</v>
@@ -2914,10 +2877,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C34" t="n">
         <v>-0.0716807593299764</v>
@@ -2946,10 +2909,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C35" t="n">
         <v>0.0756736130579796</v>
@@ -2978,10 +2941,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
         <v>-0.36632543701146</v>
@@ -3010,10 +2973,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C37" t="n">
         <v>0.641811105409988</v>
@@ -3042,10 +3005,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C38" t="n">
         <v>0.738136204662758</v>
@@ -3074,10 +3037,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C39" t="n">
         <v>-0.266842208228013</v>
@@ -3106,10 +3069,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
         <v>0.727620639313635</v>
@@ -3138,10 +3101,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C41" t="n">
         <v>0.367818535974343</v>
@@ -3170,10 +3133,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
         <v>-0.283930106182109</v>
@@ -3202,10 +3165,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C43" t="n">
         <v>0.319624924190982</v>
@@ -3234,10 +3197,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C44" t="n">
         <v>0.132730461644487</v>
@@ -3266,10 +3229,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
         <v>0.690184686282777</v>
@@ -3298,10 +3261,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C46" t="n">
         <v>-0.0235163908202505</v>
@@ -3330,10 +3293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C47" t="n">
         <v>-0.231466571428472</v>
@@ -3362,10 +3325,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C48" t="n">
         <v>-0.0740664593009344</v>
@@ -3394,10 +3357,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C49" t="n">
         <v>0.182572976132509</v>
@@ -3426,10 +3389,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
         <v>0.0115497817547735</v>
@@ -3458,10 +3421,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C51" t="n">
         <v>0.34585681895223</v>
@@ -3490,10 +3453,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C52" t="n">
         <v>0.756486589817346</v>
@@ -3522,10 +3485,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C53" t="n">
         <v>0.757432378927848</v>
@@ -3554,10 +3517,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C54" t="n">
         <v>0.379249850448376</v>
@@ -3586,10 +3549,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C55" t="n">
         <v>-0.152864126063924</v>
@@ -3618,10 +3581,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C56" t="n">
         <v>-0.123307935845685</v>
@@ -3650,10 +3613,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C57" t="n">
         <v>-0.443990008313466</v>
@@ -3682,10 +3645,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C58" t="n">
         <v>0.0503405688609349</v>
@@ -3714,10 +3677,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C59" t="n">
         <v>-0.236741559277705</v>
@@ -3746,10 +3709,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C60" t="n">
         <v>-0.104603623396612</v>
@@ -3778,10 +3741,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C61" t="n">
         <v>-0.32536923451631</v>
@@ -3810,10 +3773,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C62" t="n">
         <v>-0.132296636890081</v>
@@ -3842,10 +3805,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C63" t="n">
         <v>-0.262028092023339</v>
@@ -3874,10 +3837,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C64" t="n">
         <v>-0.145024015670317</v>
@@ -3906,10 +3869,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C65" t="n">
         <v>0.662634190325809</v>
@@ -3938,10 +3901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C66" t="n">
         <v>-0.275364261279887</v>
@@ -3970,10 +3933,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C67" t="n">
         <v>-0.164352258957285</v>
@@ -4002,10 +3965,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C68" t="n">
         <v>0.0885372373217003</v>
@@ -4034,10 +3997,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C69" t="n">
         <v>-0.109042366689391</v>
@@ -4066,10 +4029,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C70" t="n">
         <v>0.319069283633091</v>
@@ -4098,10 +4061,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C71" t="n">
         <v>-0.331719219278336</v>
@@ -4130,10 +4093,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C72" t="n">
         <v>-0.244092606980222</v>
@@ -4162,10 +4125,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C73" t="n">
         <v>0.571867526904049</v>
@@ -4194,10 +4157,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C74" t="n">
         <v>-0.203272735223298</v>
@@ -4226,10 +4189,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C75" t="n">
         <v>-0.251730509283895</v>
@@ -4258,10 +4221,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C76" t="n">
         <v>0.912353543118443</v>
@@ -4290,10 +4253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C77" t="n">
         <v>-0.22358997998478</v>
@@ -4322,10 +4285,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C78" t="n">
         <v>0.0969126702382847</v>
@@ -4354,10 +4317,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
         <v>-0.33805169489112</v>
@@ -4397,42 +4360,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>54</v>
-      </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B2" t="n">
         <v>394</v>
@@ -4441,33 +4404,33 @@
         <v>363</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1197</v>
+        <v>-2.3508</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5761</v>
+        <v>-1.4809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6957</v>
+        <v>0.8699</v>
       </c>
       <c r="G2" t="n">
-        <v>4.96</v>
+        <v>7.41</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000698727580091085</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B3" t="n">
         <v>394</v>
@@ -4476,33 +4439,33 @@
         <v>363</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.3404</v>
+        <v>-2.6519</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7751</v>
+        <v>-1.9742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5652</v>
+        <v>0.6777</v>
       </c>
       <c r="G3" t="n">
-        <v>3.67</v>
+        <v>4.76</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000434304567007542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B4" t="n">
         <v>394</v>
@@ -4511,33 +4474,33 @@
         <v>363</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9917</v>
+        <v>0.0545</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1126</v>
+        <v>-0.5609</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1043</v>
+        <v>-0.6153</v>
       </c>
       <c r="G4" t="n">
-        <v>12.71</v>
+        <v>0.24</v>
       </c>
       <c r="H4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000742776091162948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000350165871548247</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B5" t="n">
         <v>394</v>
@@ -4546,33 +4509,33 @@
         <v>363</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9894</v>
+        <v>3.2896</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5746</v>
+        <v>2.7319</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4148</v>
+        <v>-0.5577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000198232734348008</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503206171806483</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B6" t="n">
         <v>394</v>
@@ -4581,33 +4544,33 @@
         <v>363</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1939</v>
+        <v>-3.2896</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6139</v>
+        <v>-2.7319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.42</v>
+        <v>0.5577</v>
       </c>
       <c r="G6" t="n">
-        <v>2.63</v>
+        <v>3.61</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000411</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000198232734348008</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503206171806483</v>
       </c>
       <c r="K6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B7" t="n">
         <v>394</v>
@@ -4616,33 +4579,33 @@
         <v>363</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3912</v>
+        <v>-3.4146</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0831</v>
+        <v>-2.8671</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4743</v>
+        <v>0.5475</v>
       </c>
       <c r="G7" t="n">
-        <v>0.34</v>
+        <v>3.53</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000408</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000162221725106145</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000334582308031423</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B8" t="n">
         <v>394</v>
@@ -4651,33 +4614,33 @@
         <v>363</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1853</v>
+        <v>1.0696</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6258</v>
+        <v>0.5529</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4406</v>
+        <v>-0.5166</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>0.3</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000305103479302289</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000457655218953433</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B9" t="n">
         <v>394</v>
@@ -4686,33 +4649,33 @@
         <v>363</v>
       </c>
       <c r="D9" t="n">
-        <v>1.273</v>
+        <v>2.9812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3728</v>
+        <v>2.4728</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9001</v>
+        <v>-0.5084</v>
       </c>
       <c r="G9" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000489</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000953196439177417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000185032249957969</v>
       </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B10" t="n">
         <v>394</v>
@@ -4721,33 +4684,33 @@
         <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0209</v>
+        <v>3.0251</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5475</v>
+        <v>2.5284</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5266</v>
+        <v>-0.4967</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000427</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000550195339798033</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000864592676825481</v>
       </c>
       <c r="K10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B11" t="n">
         <v>394</v>
@@ -4756,33 +4719,33 @@
         <v>363</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2119</v>
+        <v>-3.0251</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2414</v>
+        <v>-2.5284</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9705</v>
+        <v>0.4967</v>
       </c>
       <c r="G11" t="n">
-        <v>9.34</v>
+        <v>3.14</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000478</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000550195339798033</v>
       </c>
       <c r="J11" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000864592676825481</v>
       </c>
       <c r="K11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B12" t="n">
         <v>394</v>
@@ -4791,33 +4754,33 @@
         <v>363</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.273</v>
+        <v>2.6541</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3728</v>
+        <v>2.1757</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9001</v>
+        <v>-0.4784</v>
       </c>
       <c r="G12" t="n">
-        <v>7.95</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000489</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000252069610214062</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000147</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000437805112477056</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B13" t="n">
         <v>394</v>
@@ -4826,33 +4789,33 @@
         <v>363</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8547</v>
+        <v>1.4829</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0941</v>
+        <v>1.0304</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9488</v>
+        <v>-0.4525</v>
       </c>
       <c r="G13" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000611</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000238385115225527</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000342030817497495</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B14" t="n">
         <v>394</v>
@@ -4861,33 +4824,33 @@
         <v>363</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8636</v>
+        <v>-0.8638</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0403</v>
+        <v>-0.4587</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8233</v>
+        <v>0.4051</v>
       </c>
       <c r="G14" t="n">
-        <v>0.15</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000819</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407611296574457</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K14" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B15" t="n">
         <v>394</v>
@@ -4896,33 +4859,33 @@
         <v>363</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9341</v>
+        <v>0.305</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1775</v>
+        <v>0.6879</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7566</v>
+        <v>0.3828</v>
       </c>
       <c r="G15" t="n">
-        <v>0.18</v>
+        <v>2.41</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000838</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000845015956850821</v>
       </c>
       <c r="J15" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" t="n">
         <v>394</v>
@@ -4931,33 +4894,33 @@
         <v>363</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9546</v>
+        <v>0.2644</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3722</v>
+        <v>0.6418</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5825</v>
+        <v>0.3774</v>
       </c>
       <c r="G16" t="n">
-        <v>3.82</v>
+        <v>2.38</v>
       </c>
       <c r="H16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000727</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000262273675821503</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000865503130210961</v>
       </c>
       <c r="K16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B17" t="n">
         <v>394</v>
@@ -4966,33 +4929,33 @@
         <v>363</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9341</v>
+        <v>-3.732</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1775</v>
+        <v>-3.3567</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7566</v>
+        <v>0.3753</v>
       </c>
       <c r="G17" t="n">
-        <v>5.71</v>
+        <v>2.37</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000838</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168706658373603</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000173</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503206171806483</v>
       </c>
       <c r="K17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B18" t="n">
         <v>394</v>
@@ -5001,33 +4964,33 @@
         <v>363</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.313</v>
+        <v>0.0674</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0297</v>
+        <v>-0.3073</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2833</v>
+        <v>-0.3747</v>
       </c>
       <c r="G18" t="n">
-        <v>1.92</v>
+        <v>0.42</v>
       </c>
       <c r="H18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000224</v>
+        <v>0.000000000000000000000000000000000000000681121390859979</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000434</v>
+        <v>0.000000000000000000000000000000000000000725064706399332</v>
       </c>
       <c r="K18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B19" t="n">
         <v>394</v>
@@ -5036,33 +4999,33 @@
         <v>363</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0268</v>
+        <v>-1.1404</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7447</v>
+        <v>-0.8154</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.282</v>
+        <v>0.3251</v>
       </c>
       <c r="G19" t="n">
-        <v>0.52</v>
+        <v>2.11</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000275</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000223826440863733</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000453</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000410348474916844</v>
       </c>
       <c r="K19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B20" t="n">
         <v>394</v>
@@ -5071,33 +5034,33 @@
         <v>363</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8195</v>
+        <v>1.3697</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4001</v>
+        <v>1.0485</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4194</v>
+        <v>-0.3212</v>
       </c>
       <c r="G20" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="H20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000026</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000294455211529457</v>
       </c>
       <c r="J20" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000453</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000121462774755901</v>
       </c>
       <c r="K20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B21" t="n">
         <v>394</v>
@@ -5106,33 +5069,33 @@
         <v>363</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0268</v>
+        <v>0.9442</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7447</v>
+        <v>1.2607</v>
       </c>
       <c r="F21" t="n">
-        <v>0.282</v>
+        <v>0.3165</v>
       </c>
       <c r="G21" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="H21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000275</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000180149099655061</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000453</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000424637163472643</v>
       </c>
       <c r="K21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B22" t="n">
         <v>394</v>
@@ -5141,33 +5104,33 @@
         <v>363</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4076</v>
+        <v>-0.7381</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7711</v>
+        <v>-0.4819</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1787</v>
+        <v>0.2562</v>
       </c>
       <c r="G22" t="n">
-        <v>0.07</v>
+        <v>1.8</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I22" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000459</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000840191745485496</v>
       </c>
       <c r="J22" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000721</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000115526365004256</v>
       </c>
       <c r="K22" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B23" t="n">
         <v>394</v>
@@ -5176,33 +5139,33 @@
         <v>363</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1665</v>
+        <v>-0.3203</v>
       </c>
       <c r="E23" t="n">
-        <v>0.521</v>
+        <v>-0.0862</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6455</v>
+        <v>0.2341</v>
       </c>
       <c r="G23" t="n">
-        <v>0.23</v>
+        <v>1.71</v>
       </c>
       <c r="H23" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000568</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000193966572888018</v>
       </c>
       <c r="J23" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000852</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000010668161508841</v>
       </c>
       <c r="K23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B24" t="n">
         <v>394</v>
@@ -5211,33 +5174,33 @@
         <v>363</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1859</v>
+        <v>-0.3585</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5005</v>
+        <v>-0.1347</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6854</v>
+        <v>0.2237</v>
       </c>
       <c r="G24" t="n">
-        <v>0.21</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000108</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000151448458936993</v>
       </c>
       <c r="J24" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000154</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000199911965796831</v>
       </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B25" t="n">
         <v>394</v>
@@ -5246,33 +5209,33 @@
         <v>363</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0552</v>
+        <v>0.5371</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3036</v>
+        <v>0.3727</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3589</v>
+        <v>-0.1644</v>
       </c>
       <c r="G25" t="n">
-        <v>2.29</v>
+        <v>0.68</v>
       </c>
       <c r="H25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000754</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000411175586756774</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000104</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000904586290864904</v>
       </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B26" t="n">
         <v>394</v>
@@ -5281,33 +5244,33 @@
         <v>363</v>
       </c>
       <c r="D26" t="n">
-        <v>1.0449</v>
+        <v>2.6039</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7259</v>
+        <v>2.4503</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3189</v>
+        <v>-0.1536</v>
       </c>
       <c r="G26" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000152</v>
+        <v>0.0000000000130895411819585</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000201</v>
+        <v>0.0000000000130895411819585</v>
       </c>
       <c r="K26" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B27" t="n">
         <v>394</v>
@@ -5316,33 +5279,33 @@
         <v>363</v>
       </c>
       <c r="D27" t="n">
-        <v>1.0989</v>
+        <v>-0.9657</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5427</v>
+        <v>-0.8456</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5562</v>
+        <v>0.1201</v>
       </c>
       <c r="G27" t="n">
-        <v>0.28</v>
+        <v>1.32</v>
       </c>
       <c r="H27" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I27" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000355</v>
+        <v>0.00000000000000000000000000000000000242971859004497</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000045</v>
+        <v>0.00000000000000000000000000000000000250564729598388</v>
       </c>
       <c r="K27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B28" t="n">
         <v>394</v>
@@ -5351,33 +5314,33 @@
         <v>363</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.1781</v>
+        <v>1.0029</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.739</v>
+        <v>1.1186</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4391</v>
+        <v>0.1156</v>
       </c>
       <c r="G28" t="n">
-        <v>2.75</v>
+        <v>1.31</v>
       </c>
       <c r="H28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000402</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000630344484191873</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000491</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000557710531521542</v>
       </c>
       <c r="K28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B29" t="n">
         <v>394</v>
@@ -5386,33 +5349,33 @@
         <v>363</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.336</v>
+        <v>1.9396</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9039</v>
+        <v>1.8312</v>
       </c>
       <c r="F29" t="n">
-        <v>0.432</v>
+        <v>-0.1084</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7</v>
+        <v>0.78</v>
       </c>
       <c r="H29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000217</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000317163919330143</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000256</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000037380033349624</v>
       </c>
       <c r="K29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B30" t="n">
         <v>394</v>
@@ -5421,33 +5384,33 @@
         <v>363</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3783</v>
+        <v>-1.9396</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0445</v>
+        <v>-1.8312</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3338</v>
+        <v>0.1084</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>1.28</v>
       </c>
       <c r="H30" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I30" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000617</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000317163919330143</v>
       </c>
       <c r="J30" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000702</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000037380033349624</v>
       </c>
       <c r="K30" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B31" t="n">
         <v>394</v>
@@ -5456,33 +5419,33 @@
         <v>363</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6692</v>
+        <v>0.9718</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5416</v>
+        <v>1.0668</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1276</v>
+        <v>0.095</v>
       </c>
       <c r="G31" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="H31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I31" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000153</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000022333358323258</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000168</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000818889805186127</v>
       </c>
       <c r="K31" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B32" t="n">
         <v>394</v>
@@ -5491,33 +5454,33 @@
         <v>363</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7866</v>
+        <v>0.7732</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2486</v>
+        <v>0.6828</v>
       </c>
       <c r="F32" t="n">
-        <v>0.462</v>
+        <v>-0.0904</v>
       </c>
       <c r="G32" t="n">
-        <v>2.9</v>
+        <v>0.81</v>
       </c>
       <c r="H32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000721</v>
+        <v>0.00000000000000000000000000000000000000000113098465710804</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000768</v>
+        <v>0.00000000000000000000000000000000000000000124408312281885</v>
       </c>
       <c r="K32" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B33" t="n">
         <v>394</v>
@@ -5526,33 +5489,33 @@
         <v>363</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9913</v>
+        <v>-1.5061</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1249</v>
+        <v>-1.4378</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1336</v>
+        <v>0.0684</v>
       </c>
       <c r="G33" t="n">
-        <v>0.74</v>
+        <v>1.17</v>
       </c>
       <c r="H33" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0000000000000000000000000000000000000000000221</v>
+        <v>0.000000000000000000000000000000000000000000000000000000893758586834825</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0000000000000000000000000000000000000000000228</v>
+        <v>0.0000000000000000000000000000000000000000000000000000010170356332948</v>
       </c>
       <c r="K33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B34" t="n">
         <v>394</v>
@@ -5561,28 +5524,28 @@
         <v>363</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.2926</v>
+        <v>-1.4063</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1773</v>
+        <v>-1.4593</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1154</v>
+        <v>-0.053</v>
       </c>
       <c r="G34" t="n">
-        <v>1.3</v>
+        <v>0.89</v>
       </c>
       <c r="H34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0000000000000000644</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000110225325889987</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0000000000000000644</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000139901375168061</v>
       </c>
       <c r="K34" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -5601,30 +5564,30 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>7.18645754023726</v>
@@ -5632,16 +5595,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
         <v>2.62010333422383</v>
@@ -5649,16 +5612,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0.8389980708298</v>
@@ -5666,16 +5629,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
         <v>0.813203301164064</v>
@@ -5683,16 +5646,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
         <v>0.33120328489112</v>
@@ -5700,16 +5663,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>0.278673332782869</v>
@@ -5717,16 +5680,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>0.273301697605129</v>
@@ -5734,16 +5697,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E9" t="n">
         <v>0.210978463326721</v>
@@ -5751,16 +5714,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
         <v>0.199226499645656</v>
@@ -5768,16 +5731,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
         <v>0.147896479033864</v>
@@ -5785,16 +5748,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>2.37773618164618</v>
@@ -5802,16 +5765,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
         <v>1.34952567052801</v>
@@ -5819,16 +5782,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
         <v>0.6709017113054</v>
@@ -5836,16 +5799,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
         <v>0.339022844487245</v>
@@ -5853,16 +5816,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>0.214143723353137</v>
@@ -5870,16 +5833,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
         <v>0.207140952755415</v>
@@ -5887,16 +5850,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B18" t="n">
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
         <v>0.172061365524471</v>
@@ -5904,16 +5867,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E19" t="n">
         <v>0.141897120962924</v>
@@ -5921,16 +5884,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E20" t="n">
         <v>0.124138007811942</v>
@@ -5938,16 +5901,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B21" t="n">
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E21" t="n">
         <v>0.0947997803962724</v>
